--- a/02_server_update/logs/unedited_photos.xlsx
+++ b/02_server_update/logs/unedited_photos.xlsx
@@ -427,16 +427,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="208" customWidth="1" min="6" max="6"/>
+    <col width="216" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -490,17 +490,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AXC</t>
+          <t>CATUDAYA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ZP 28C BTT-BOP</t>
+          <t>BATTERE ER SINYAL CGB</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>50.jpg</t>
+          <t>0.jpg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -510,17 +510,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>D:\Dika\IMO\MEI\FOTO\03_export_foto\BTP BD\AXC\ZP 28C BTT-BOP\50.jpg</t>
+          <t>D:\Dika\IMO\DAOP 1\4. APRIL\RESOR STL 1.21 BOGOR\2. BPBYE Perawatan Berkala Persinyalan Elektrik\14. BPBYE14 Perawatan Catu Daya 1 (satu) Bulanan\03_export_foto\BTP BD\CATUDAYA\BATTERE ER SINYAL CGB\0.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>D:\Dika\IMO\MEI\FOTO\04_photos_edited\Tim_1\BTP BD\AXC\ZP 28C BTT-BOP\50.jpg</t>
+          <t>D:\Dika\IMO\DAOP 1\4. APRIL\RESOR STL 1.21 BOGOR\2. BPBYE Perawatan Berkala Persinyalan Elektrik\14. BPBYE14 Perawatan Catu Daya 1 (satu) Bulanan\04_photos_edited\Tim_1\BTP BD\CATUDAYA\BATTERE ER SINYAL CGB\0.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-25 01:47:48</t>
+          <t>2026-10-28 22:34:56</t>
         </is>
       </c>
     </row>
@@ -532,37 +532,331 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AXC</t>
+          <t>CATUDAYA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ZP 47D BOP</t>
+          <t>BATTERE ER SINYAL CGB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>100.jpg</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>stage_fallback_skipped</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>D:\Dika\IMO\DAOP 1\4. APRIL\RESOR STL 1.21 BOGOR\2. BPBYE Perawatan Berkala Persinyalan Elektrik\14. BPBYE14 Perawatan Catu Daya 1 (satu) Bulanan\03_export_foto\BTP BD\CATUDAYA\BATTERE ER SINYAL CGB\100.jpg</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>D:\Dika\IMO\DAOP 1\4. APRIL\RESOR STL 1.21 BOGOR\2. BPBYE Perawatan Berkala Persinyalan Elektrik\14. BPBYE14 Perawatan Catu Daya 1 (satu) Bulanan\04_photos_edited\Tim_1\BTP BD\CATUDAYA\BATTERE ER SINYAL CGB\100.jpg</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:34:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BTP BD</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CATUDAYA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BATTERE ER SINYAL CGB</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>50.jpg</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>stage_fallback_skipped</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>D:\Dika\IMO\DAOP 1\4. APRIL\RESOR STL 1.21 BOGOR\2. BPBYE Perawatan Berkala Persinyalan Elektrik\14. BPBYE14 Perawatan Catu Daya 1 (satu) Bulanan\03_export_foto\BTP BD\CATUDAYA\BATTERE ER SINYAL CGB\50.jpg</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>D:\Dika\IMO\DAOP 1\4. APRIL\RESOR STL 1.21 BOGOR\2. BPBYE Perawatan Berkala Persinyalan Elektrik\14. BPBYE14 Perawatan Catu Daya 1 (satu) Bulanan\04_photos_edited\Tim_1\BTP BD\CATUDAYA\BATTERE ER SINYAL CGB\50.jpg</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:34:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BTP BD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CATUDAYA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GENSET ER SINYAL CGB</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>0.jpg</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>stage_fallback_skipped</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>D:\Dika\IMO\MEI\FOTO\03_export_foto\BTP BD\AXC\ZP 47D BOP\0.jpg</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>D:\Dika\IMO\MEI\FOTO\04_photos_edited\Tim_2\BTP BD\AXC\ZP 47D BOP\0.jpg</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-10-25 01:47:50</t>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>D:\Dika\IMO\DAOP 1\4. APRIL\RESOR STL 1.21 BOGOR\2. BPBYE Perawatan Berkala Persinyalan Elektrik\14. BPBYE14 Perawatan Catu Daya 1 (satu) Bulanan\03_export_foto\BTP BD\CATUDAYA\GENSET ER SINYAL CGB\0.jpg</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>D:\Dika\IMO\DAOP 1\4. APRIL\RESOR STL 1.21 BOGOR\2. BPBYE Perawatan Berkala Persinyalan Elektrik\14. BPBYE14 Perawatan Catu Daya 1 (satu) Bulanan\04_photos_edited\Tim_1\BTP BD\CATUDAYA\GENSET ER SINYAL CGB\0.jpg</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:34:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BTP BD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CATUDAYA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GENSET ER SINYAL CGB</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>100.jpg</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>stage_fallback_skipped</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>D:\Dika\IMO\DAOP 1\4. APRIL\RESOR STL 1.21 BOGOR\2. BPBYE Perawatan Berkala Persinyalan Elektrik\14. BPBYE14 Perawatan Catu Daya 1 (satu) Bulanan\03_export_foto\BTP BD\CATUDAYA\GENSET ER SINYAL CGB\100.jpg</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>D:\Dika\IMO\DAOP 1\4. APRIL\RESOR STL 1.21 BOGOR\2. BPBYE Perawatan Berkala Persinyalan Elektrik\14. BPBYE14 Perawatan Catu Daya 1 (satu) Bulanan\04_photos_edited\Tim_1\BTP BD\CATUDAYA\GENSET ER SINYAL CGB\100.jpg</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:34:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BTP BD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CATUDAYA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GENSET ER SINYAL CGB</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>50.jpg</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>stage_fallback_skipped</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>D:\Dika\IMO\DAOP 1\4. APRIL\RESOR STL 1.21 BOGOR\2. BPBYE Perawatan Berkala Persinyalan Elektrik\14. BPBYE14 Perawatan Catu Daya 1 (satu) Bulanan\03_export_foto\BTP BD\CATUDAYA\GENSET ER SINYAL CGB\50.jpg</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>D:\Dika\IMO\DAOP 1\4. APRIL\RESOR STL 1.21 BOGOR\2. BPBYE Perawatan Berkala Persinyalan Elektrik\14. BPBYE14 Perawatan Catu Daya 1 (satu) Bulanan\04_photos_edited\Tim_1\BTP BD\CATUDAYA\GENSET ER SINYAL CGB\50.jpg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:34:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BTP BD</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CATUDAYA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>UPS ER SINYAL CGB</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.jpg</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>stage_fallback_skipped</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>D:\Dika\IMO\DAOP 1\4. APRIL\RESOR STL 1.21 BOGOR\2. BPBYE Perawatan Berkala Persinyalan Elektrik\14. BPBYE14 Perawatan Catu Daya 1 (satu) Bulanan\03_export_foto\BTP BD\CATUDAYA\UPS ER SINYAL CGB\0.jpg</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>D:\Dika\IMO\DAOP 1\4. APRIL\RESOR STL 1.21 BOGOR\2. BPBYE Perawatan Berkala Persinyalan Elektrik\14. BPBYE14 Perawatan Catu Daya 1 (satu) Bulanan\04_photos_edited\Tim_1\BTP BD\CATUDAYA\UPS ER SINYAL CGB\0.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:35:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BTP BD</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CATUDAYA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>UPS ER SINYAL CGB</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>100.jpg</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>stage_fallback_skipped</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>D:\Dika\IMO\DAOP 1\4. APRIL\RESOR STL 1.21 BOGOR\2. BPBYE Perawatan Berkala Persinyalan Elektrik\14. BPBYE14 Perawatan Catu Daya 1 (satu) Bulanan\03_export_foto\BTP BD\CATUDAYA\UPS ER SINYAL CGB\100.jpg</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>D:\Dika\IMO\DAOP 1\4. APRIL\RESOR STL 1.21 BOGOR\2. BPBYE Perawatan Berkala Persinyalan Elektrik\14. BPBYE14 Perawatan Catu Daya 1 (satu) Bulanan\04_photos_edited\Tim_1\BTP BD\CATUDAYA\UPS ER SINYAL CGB\100.jpg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:35:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BTP BD</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CATUDAYA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>UPS ER SINYAL CGB</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>50.jpg</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>stage_fallback_skipped</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>D:\Dika\IMO\DAOP 1\4. APRIL\RESOR STL 1.21 BOGOR\2. BPBYE Perawatan Berkala Persinyalan Elektrik\14. BPBYE14 Perawatan Catu Daya 1 (satu) Bulanan\03_export_foto\BTP BD\CATUDAYA\UPS ER SINYAL CGB\50.jpg</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>D:\Dika\IMO\DAOP 1\4. APRIL\RESOR STL 1.21 BOGOR\2. BPBYE Perawatan Berkala Persinyalan Elektrik\14. BPBYE14 Perawatan Catu Daya 1 (satu) Bulanan\04_photos_edited\Tim_1\BTP BD\CATUDAYA\UPS ER SINYAL CGB\50.jpg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:35:01</t>
         </is>
       </c>
     </row>
